--- a/tests/fixtures/rc_automation/all-in-one xlsx sheet needed like this example.xlsx
+++ b/tests/fixtures/rc_automation/all-in-one xlsx sheet needed like this example.xlsx
@@ -8,24 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ZAID\Advance AI\pyRevit-addons\tests\fixtures\rc_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4D4BEEB-A2C6-4A7B-B88B-6F4A374849F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832723B1-2AF4-48E8-8D20-DFD61426969C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15660" firstSheet="1" activeTab="1" xr2:uid="{05CF64EA-22C0-42D7-B8E7-B385C12F575E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15660" activeTab="5" xr2:uid="{05CF64EA-22C0-42D7-B8E7-B385C12F575E}"/>
   </bookViews>
   <sheets>
-    <sheet name="COLUMN_REBAR" sheetId="2" r:id="rId1"/>
-    <sheet name="FOOTING_TYPES" sheetId="6" r:id="rId2"/>
-    <sheet name="FOOTING_REBAR" sheetId="5" r:id="rId3"/>
-    <sheet name="FOOTING_PLACEMENT" sheetId="4" r:id="rId4"/>
-    <sheet name="COLUMN_TYPES" sheetId="3" r:id="rId5"/>
-    <sheet name="COLUMN_PLACEMENT" sheetId="1" r:id="rId6"/>
+    <sheet name="COLUMN_TYPES" sheetId="3" r:id="rId1"/>
+    <sheet name="COLUMN_PLACEMENT" sheetId="1" r:id="rId2"/>
+    <sheet name="COLUMN_REBAR" sheetId="2" r:id="rId3"/>
+    <sheet name="FOOTING_TYPES" sheetId="6" r:id="rId4"/>
+    <sheet name="FOOTING_PLACEMENT" sheetId="4" r:id="rId5"/>
+    <sheet name="FOOTING_REBAR" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="5" hidden="1">'COLUMN_PLACEMENT'!$A$1:$K$6</definedName>
-    <definedName name="ExternalData_2" localSheetId="0" hidden="1">'COLUMN_REBAR'!$A$1:$J$8</definedName>
-    <definedName name="ExternalData_2" localSheetId="4" hidden="1">'COLUMN_TYPES'!$A$1:$F$4</definedName>
-    <definedName name="ExternalData_3" localSheetId="3" hidden="1">FOOTING_PLACEMENT!$A$1:$J$7</definedName>
-    <definedName name="ExternalData_4" localSheetId="2" hidden="1">FOOTING_REBAR!$A$1:$J$11</definedName>
+    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'COLUMN_PLACEMENT'!$A$1:$K$6</definedName>
+    <definedName name="ExternalData_2" localSheetId="2" hidden="1">'COLUMN_REBAR'!$A$1:$J$8</definedName>
+    <definedName name="ExternalData_2" localSheetId="0" hidden="1">'COLUMN_TYPES'!$A$1:$F$4</definedName>
+    <definedName name="ExternalData_3" localSheetId="4" hidden="1">FOOTING_PLACEMENT!$A$1:$J$7</definedName>
+    <definedName name="ExternalData_4" localSheetId="5" hidden="1">FOOTING_REBAR!$A$1:$J$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -381,17 +381,174 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="36">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -425,166 +582,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -599,63 +596,6 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" connectionId="2" xr16:uid="{3D391ED9-E8C2-4CC9-8B27-855B97D2F5AD}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="11">
-    <queryTableFields count="10">
-      <queryTableField id="1" name="TypeMark" tableColumnId="1"/>
-      <queryTableField id="2" name="BarRole" tableColumnId="2"/>
-      <queryTableField id="3" name="BarType" tableColumnId="3"/>
-      <queryTableField id="4" name="Diameter" tableColumnId="4"/>
-      <queryTableField id="5" name="Count" tableColumnId="5"/>
-      <queryTableField id="6" name="Spacing" tableColumnId="6"/>
-      <queryTableField id="7" name="ShapeCode" tableColumnId="7"/>
-      <queryTableField id="8" name="SpacingEnd" tableColumnId="8"/>
-      <queryTableField id="9" name="ConfinementLength" tableColumnId="9"/>
-      <queryTableField id="10" name="Comments" tableColumnId="10"/>
-    </queryTableFields>
-  </queryTableRefresh>
-</queryTable>
-</file>
-
-<file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_4" connectionId="5" xr16:uid="{0A49FF99-2B01-40CB-A8A5-4A447B0F497C}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="11">
-    <queryTableFields count="10">
-      <queryTableField id="1" name="TypeMark" tableColumnId="1"/>
-      <queryTableField id="2" name="Layer" tableColumnId="2"/>
-      <queryTableField id="3" name="Direction" tableColumnId="3"/>
-      <queryTableField id="4" name="BarType" tableColumnId="4"/>
-      <queryTableField id="5" name="Diameter" tableColumnId="5"/>
-      <queryTableField id="6" name="Count" tableColumnId="6"/>
-      <queryTableField id="7" name="Spacing" tableColumnId="7"/>
-      <queryTableField id="8" name="ShapeCode" tableColumnId="8"/>
-      <queryTableField id="9" name="EndCover" tableColumnId="9"/>
-      <queryTableField id="10" name="Comments" tableColumnId="10"/>
-    </queryTableFields>
-  </queryTableRefresh>
-</queryTable>
-</file>
-
-<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_3" connectionId="4" xr16:uid="{9DF0BE04-8029-425F-986A-A8CC358779BC}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="11">
-    <queryTableFields count="10">
-      <queryTableField id="1" name="Mark" tableColumnId="1"/>
-      <queryTableField id="2" name="TypeMark" tableColumnId="2"/>
-      <queryTableField id="3" name="GridX" tableColumnId="3"/>
-      <queryTableField id="4" name="GridY" tableColumnId="4"/>
-      <queryTableField id="5" name="X" tableColumnId="5"/>
-      <queryTableField id="6" name="Y" tableColumnId="6"/>
-      <queryTableField id="7" name="Level" tableColumnId="7"/>
-      <queryTableField id="8" name="TopOffset" tableColumnId="8"/>
-      <queryTableField id="9" name="Rotation" tableColumnId="9"/>
-      <queryTableField id="10" name="Outline" tableColumnId="10"/>
-    </queryTableFields>
-  </queryTableRefresh>
-</queryTable>
-</file>
-
-<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" connectionId="3" xr16:uid="{AFF25E43-918F-4CB1-A380-7D17B31F78A9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="7">
     <queryTableFields count="6">
@@ -670,7 +610,7 @@
 </queryTable>
 </file>
 
-<file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{8C66B5B2-45AA-41E9-A8EB-E955471EDB82}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="12">
     <queryTableFields count="11">
@@ -690,113 +630,170 @@
 </queryTable>
 </file>
 
+<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" connectionId="2" xr16:uid="{3D391ED9-E8C2-4CC9-8B27-855B97D2F5AD}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="11">
+    <queryTableFields count="10">
+      <queryTableField id="1" name="TypeMark" tableColumnId="1"/>
+      <queryTableField id="2" name="BarRole" tableColumnId="2"/>
+      <queryTableField id="3" name="BarType" tableColumnId="3"/>
+      <queryTableField id="4" name="Diameter" tableColumnId="4"/>
+      <queryTableField id="5" name="Count" tableColumnId="5"/>
+      <queryTableField id="6" name="Spacing" tableColumnId="6"/>
+      <queryTableField id="7" name="ShapeCode" tableColumnId="7"/>
+      <queryTableField id="8" name="SpacingEnd" tableColumnId="8"/>
+      <queryTableField id="9" name="ConfinementLength" tableColumnId="9"/>
+      <queryTableField id="10" name="Comments" tableColumnId="10"/>
+    </queryTableFields>
+  </queryTableRefresh>
+</queryTable>
+</file>
+
+<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_3" connectionId="4" xr16:uid="{9DF0BE04-8029-425F-986A-A8CC358779BC}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="11">
+    <queryTableFields count="10">
+      <queryTableField id="1" name="Mark" tableColumnId="1"/>
+      <queryTableField id="2" name="TypeMark" tableColumnId="2"/>
+      <queryTableField id="3" name="GridX" tableColumnId="3"/>
+      <queryTableField id="4" name="GridY" tableColumnId="4"/>
+      <queryTableField id="5" name="X" tableColumnId="5"/>
+      <queryTableField id="6" name="Y" tableColumnId="6"/>
+      <queryTableField id="7" name="Level" tableColumnId="7"/>
+      <queryTableField id="8" name="TopOffset" tableColumnId="8"/>
+      <queryTableField id="9" name="Rotation" tableColumnId="9"/>
+      <queryTableField id="10" name="Outline" tableColumnId="10"/>
+    </queryTableFields>
+  </queryTableRefresh>
+</queryTable>
+</file>
+
+<file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_4" connectionId="5" xr16:uid="{0A49FF99-2B01-40CB-A8A5-4A447B0F497C}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="11">
+    <queryTableFields count="10">
+      <queryTableField id="1" name="TypeMark" tableColumnId="1"/>
+      <queryTableField id="2" name="Layer" tableColumnId="2"/>
+      <queryTableField id="3" name="Direction" tableColumnId="3"/>
+      <queryTableField id="4" name="BarType" tableColumnId="4"/>
+      <queryTableField id="5" name="Diameter" tableColumnId="5"/>
+      <queryTableField id="6" name="Count" tableColumnId="6"/>
+      <queryTableField id="7" name="Spacing" tableColumnId="7"/>
+      <queryTableField id="8" name="ShapeCode" tableColumnId="8"/>
+      <queryTableField id="9" name="EndCover" tableColumnId="9"/>
+      <queryTableField id="10" name="Comments" tableColumnId="10"/>
+    </queryTableFields>
+  </queryTableRefresh>
+</queryTable>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4BFE1A93-32B3-4699-9CB2-EED9CA5EFBFD}" name="COLUMN_TYPES" displayName="COLUMN_TYPES" ref="A1:F4" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:F4" xr:uid="{4BFE1A93-32B3-4699-9CB2-EED9CA5EFBFD}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{DE96B426-C585-4635-BD5D-F095E2A9D617}" uniqueName="1" name="TypeMark" queryTableFieldId="1" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{4AECC0BE-746E-4E63-8A94-4458C81B133B}" uniqueName="2" name="Width" queryTableFieldId="2"/>
+    <tableColumn id="3" xr3:uid="{29870623-69F9-4ED4-A38F-EFA831D11963}" uniqueName="3" name="Depth" queryTableFieldId="3"/>
+    <tableColumn id="4" xr3:uid="{180B5914-A489-4A9B-9CEB-18375B9D0B04}" uniqueName="4" name="Cover" queryTableFieldId="4"/>
+    <tableColumn id="5" xr3:uid="{DBFAA8F7-6959-4F3C-BFBF-AE6D07C5470E}" uniqueName="5" name="Concrete" queryTableFieldId="5" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{D3C3664E-7056-444B-9D3E-B86ABB260358}" uniqueName="6" name="Comments" queryTableFieldId="6" dataDxfId="7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{250B1DA8-FE9E-4853-82C5-5A76FE179E95}" name="COLUMN_PLACEMENT" displayName="COLUMN_PLACEMENT" ref="A1:K6" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:K6" xr:uid="{250B1DA8-FE9E-4853-82C5-5A76FE179E95}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{799DCFBF-5F41-4919-A54D-E00DAED99B97}" uniqueName="1" name="Mark" queryTableFieldId="1" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{80B953F0-3409-4AA4-BA82-AB238ED3F873}" uniqueName="2" name="TypeMark" queryTableFieldId="2" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{658A7640-46D3-405D-A3B1-2DD87F814232}" uniqueName="3" name="GridX" queryTableFieldId="3" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{28C9493F-4EDC-4DEA-A069-2EABCC8221D9}" uniqueName="4" name="GridY" queryTableFieldId="4"/>
+    <tableColumn id="5" xr3:uid="{7039779C-43C8-4AF4-9E6C-5F591BC00B6B}" uniqueName="5" name="X" queryTableFieldId="5" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{F82C3927-F4B8-449B-8F9F-52F24BA96740}" uniqueName="6" name="Y" queryTableFieldId="6" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{C2067144-F640-41CF-B84F-43A7E5ABE6AD}" uniqueName="7" name="BaseLevel" queryTableFieldId="7" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{E4F7844C-45D3-413C-AA4C-0B574CCA7D71}" uniqueName="8" name="BaseOffset" queryTableFieldId="8"/>
+    <tableColumn id="9" xr3:uid="{43F2CC9C-33CF-4BF2-A790-D4ED540ECE49}" uniqueName="9" name="TopLevel" queryTableFieldId="9" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{E5FEB261-9C6B-41E7-822D-8C3D403AE21C}" uniqueName="10" name="TopOffset" queryTableFieldId="10"/>
+    <tableColumn id="11" xr3:uid="{4DBCB596-B53A-4F0A-A83E-208B045AC6A9}" uniqueName="11" name="Rotation" queryTableFieldId="11"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0ADF4F80-1CAB-46A5-89E1-BA93AA63E5F0}" name="COLUMN_REBAR" displayName="COLUMN_REBAR" ref="A1:J8" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:J8" xr:uid="{0ADF4F80-1CAB-46A5-89E1-BA93AA63E5F0}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{6FABF50B-7AD6-4671-A4D8-7E6938C26C9A}" uniqueName="1" name="TypeMark" queryTableFieldId="1" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{56BF1CD1-6CF8-4CD0-910C-209155FB6B4C}" uniqueName="2" name="BarRole" queryTableFieldId="2" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{F4ECBBCA-9B70-4153-8794-6B971F7DDB4D}" uniqueName="3" name="BarType" queryTableFieldId="3" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{6FABF50B-7AD6-4671-A4D8-7E6938C26C9A}" uniqueName="1" name="TypeMark" queryTableFieldId="1" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{56BF1CD1-6CF8-4CD0-910C-209155FB6B4C}" uniqueName="2" name="BarRole" queryTableFieldId="2" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{F4ECBBCA-9B70-4153-8794-6B971F7DDB4D}" uniqueName="3" name="BarType" queryTableFieldId="3" dataDxfId="21"/>
     <tableColumn id="4" xr3:uid="{B0100D8D-38C1-4188-B309-33D5AA79CBA1}" uniqueName="4" name="Diameter" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{2EAD70E5-069B-476C-B07E-4439C415DB34}" uniqueName="5" name="Count" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{E28660DA-566E-41E6-82B4-B85453F9EEFB}" uniqueName="6" name="Spacing" queryTableFieldId="6"/>
     <tableColumn id="7" xr3:uid="{EC95EEF1-3832-49DF-8826-AFB242418EDB}" uniqueName="7" name="ShapeCode" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{B5C5AAC0-50C9-46BC-9AAA-DA015E47124C}" uniqueName="8" name="SpacingEnd" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{8292917D-88BD-40BA-96A3-5EFE301C8C6F}" uniqueName="9" name="ConfinementLength" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{EF2C2AEC-0E60-4465-B333-3C4FF572CCE7}" uniqueName="10" name="Comments" queryTableFieldId="10" dataDxfId="25"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E59FF54F-268A-434C-8C82-9064F7727F73}" name="FOOTING_TYPES" displayName="FOOTING_TYPES" ref="A1:I4" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" tableBorderDxfId="11">
-  <autoFilter ref="A1:I4" xr:uid="{E59FF54F-268A-434C-8C82-9064F7727F73}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{1055A2BE-E167-4DC3-8F67-F91B62158952}" name="TypeMark" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{7EB21FE8-5F16-4FC5-A2E6-41992B2F34CF}" name="Length" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{1D36A1F3-7567-4855-9E7D-9ABA466036D8}" name="Width" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{4D815AD5-242A-473B-A732-662526587E43}" name="Thickness" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{6EED3642-135F-48B1-94A1-C7FA96DBDFA1}" name="CoverTop" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{2948D62F-4A1F-4A01-9EEC-828ECDFDB5B2}" name="CoverBottom" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{8C9EBC9F-B58E-404D-A07C-7C6B5E1C1D07}" name="CoverSide" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{F944763E-0EB2-4851-BEFC-8683DAEBA987}" name="Concrete" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{1B122D20-8887-43DA-8F61-4CEF2899A814}" name="Comments" dataDxfId="2"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FD210D4A-8F35-4202-A2DB-04840A11C937}" name="FOOTING_REBAR" displayName="FOOTING_REBAR" ref="A1:J11" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:J11" xr:uid="{FD210D4A-8F35-4202-A2DB-04840A11C937}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{69AA0B57-9AC3-40CF-9E7E-1B1BDA36FDFC}" uniqueName="1" name="TypeMark" queryTableFieldId="1" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{FAFA0DF1-D8AD-46D5-A054-F5351A0755BF}" uniqueName="2" name="Layer" queryTableFieldId="2" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{4C5CAD4B-0B7F-4816-A46F-722EFAC4B5B2}" uniqueName="3" name="Direction" queryTableFieldId="3" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{6308373A-3C6F-4154-9DEA-2EADA5D91642}" uniqueName="4" name="BarType" queryTableFieldId="4" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{DB18EAED-0474-4CF5-8131-C6CA37AD7BFB}" uniqueName="5" name="Diameter" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{8FB09626-1F5B-467B-918F-791DF536BF09}" uniqueName="6" name="Count" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{CA783AEC-AFDC-433D-BC88-DEA2D10F866D}" uniqueName="7" name="Spacing" queryTableFieldId="7"/>
-    <tableColumn id="8" xr3:uid="{E1416F18-9CEB-4635-A378-C10DA1F9BBA0}" uniqueName="8" name="ShapeCode" queryTableFieldId="8"/>
-    <tableColumn id="9" xr3:uid="{80CF4E90-46B9-4EE9-AB73-283061EBE3A4}" uniqueName="9" name="EndCover" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{DE04E247-6481-46C3-BEE4-C9D8C6CCD116}" uniqueName="10" name="Comments" queryTableFieldId="10" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{EF2C2AEC-0E60-4465-B333-3C4FF572CCE7}" uniqueName="10" name="Comments" queryTableFieldId="10" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{13F0C00B-5EC5-4106-B8B7-60EAF552560E}" name="FOOTING_PLACEMENT" displayName="FOOTING_PLACEMENT" ref="A1:J7" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:J7" xr:uid="{13F0C00B-5EC5-4106-B8B7-60EAF552560E}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{E5D34BED-40D4-40F6-BB20-454779768993}" uniqueName="1" name="Mark" queryTableFieldId="1" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{8DEAD801-58E1-441F-B526-F155860CCFD3}" uniqueName="2" name="TypeMark" queryTableFieldId="2" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{8960A015-033F-48E8-80EE-B3C200976017}" uniqueName="3" name="GridX" queryTableFieldId="3" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{CCEC861C-63E7-4919-B7B5-DC1E93DF84D8}" uniqueName="4" name="GridY" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{AD212049-D09D-443A-A7E0-CC81C58DE405}" uniqueName="5" name="X" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{DDEBE742-A0DA-4E5B-B8A2-50C86982192B}" uniqueName="6" name="Y" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{B34ACDA7-47A6-44E5-8C7F-BBB8C34D5FF2}" uniqueName="7" name="Level" queryTableFieldId="7" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{C66EAA9F-1116-4CEB-A28A-34DCF6CBD4DF}" uniqueName="8" name="TopOffset" queryTableFieldId="8"/>
-    <tableColumn id="9" xr3:uid="{59FCDB14-42BB-424B-A93C-BA98D6795D9E}" uniqueName="9" name="Rotation" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{AB2BFCA1-334F-4424-BFEB-B7EDC047320F}" uniqueName="10" name="Outline" queryTableFieldId="10" dataDxfId="17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{E59FF54F-268A-434C-8C82-9064F7727F73}" name="FOOTING_TYPES" displayName="FOOTING_TYPES" ref="A1:I4" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" tableBorderDxfId="33">
+  <autoFilter ref="A1:I4" xr:uid="{E59FF54F-268A-434C-8C82-9064F7727F73}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{1055A2BE-E167-4DC3-8F67-F91B62158952}" name="TypeMark" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{7EB21FE8-5F16-4FC5-A2E6-41992B2F34CF}" name="Length" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{1D36A1F3-7567-4855-9E7D-9ABA466036D8}" name="Width" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{4D815AD5-242A-473B-A732-662526587E43}" name="Thickness" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{6EED3642-135F-48B1-94A1-C7FA96DBDFA1}" name="CoverTop" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{2948D62F-4A1F-4A01-9EEC-828ECDFDB5B2}" name="CoverBottom" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{8C9EBC9F-B58E-404D-A07C-7C6B5E1C1D07}" name="CoverSide" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{F944763E-0EB2-4851-BEFC-8683DAEBA987}" name="Concrete" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{1B122D20-8887-43DA-8F61-4CEF2899A814}" name="Comments" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4BFE1A93-32B3-4699-9CB2-EED9CA5EFBFD}" name="COLUMN_TYPES" displayName="COLUMN_TYPES" ref="A1:F4" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F4" xr:uid="{4BFE1A93-32B3-4699-9CB2-EED9CA5EFBFD}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{DE96B426-C585-4635-BD5D-F095E2A9D617}" uniqueName="1" name="TypeMark" queryTableFieldId="1" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{4AECC0BE-746E-4E63-8A94-4458C81B133B}" uniqueName="2" name="Width" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{29870623-69F9-4ED4-A38F-EFA831D11963}" uniqueName="3" name="Depth" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{180B5914-A489-4A9B-9CEB-18375B9D0B04}" uniqueName="4" name="Cover" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{DBFAA8F7-6959-4F3C-BFBF-AE6D07C5470E}" uniqueName="5" name="Concrete" queryTableFieldId="5" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{D3C3664E-7056-444B-9D3E-B86ABB260358}" uniqueName="6" name="Comments" queryTableFieldId="6" dataDxfId="22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{13F0C00B-5EC5-4106-B8B7-60EAF552560E}" name="FOOTING_PLACEMENT" displayName="FOOTING_PLACEMENT" ref="A1:J7" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:J7" xr:uid="{13F0C00B-5EC5-4106-B8B7-60EAF552560E}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{E5D34BED-40D4-40F6-BB20-454779768993}" uniqueName="1" name="Mark" queryTableFieldId="1" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{8DEAD801-58E1-441F-B526-F155860CCFD3}" uniqueName="2" name="TypeMark" queryTableFieldId="2" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{8960A015-033F-48E8-80EE-B3C200976017}" uniqueName="3" name="GridX" queryTableFieldId="3" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{CCEC861C-63E7-4919-B7B5-DC1E93DF84D8}" uniqueName="4" name="GridY" queryTableFieldId="4"/>
+    <tableColumn id="5" xr3:uid="{AD212049-D09D-443A-A7E0-CC81C58DE405}" uniqueName="5" name="X" queryTableFieldId="5"/>
+    <tableColumn id="6" xr3:uid="{DDEBE742-A0DA-4E5B-B8A2-50C86982192B}" uniqueName="6" name="Y" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{B34ACDA7-47A6-44E5-8C7F-BBB8C34D5FF2}" uniqueName="7" name="Level" queryTableFieldId="7" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{C66EAA9F-1116-4CEB-A28A-34DCF6CBD4DF}" uniqueName="8" name="TopOffset" queryTableFieldId="8"/>
+    <tableColumn id="9" xr3:uid="{59FCDB14-42BB-424B-A93C-BA98D6795D9E}" uniqueName="9" name="Rotation" queryTableFieldId="9"/>
+    <tableColumn id="10" xr3:uid="{AB2BFCA1-334F-4424-BFEB-B7EDC047320F}" uniqueName="10" name="Outline" queryTableFieldId="10" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{250B1DA8-FE9E-4853-82C5-5A76FE179E95}" name="COLUMN_PLACEMENT" displayName="COLUMN_PLACEMENT" ref="A1:K6" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:K6" xr:uid="{250B1DA8-FE9E-4853-82C5-5A76FE179E95}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{799DCFBF-5F41-4919-A54D-E00DAED99B97}" uniqueName="1" name="Mark" queryTableFieldId="1" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{80B953F0-3409-4AA4-BA82-AB238ED3F873}" uniqueName="2" name="TypeMark" queryTableFieldId="2" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{658A7640-46D3-405D-A3B1-2DD87F814232}" uniqueName="3" name="GridX" queryTableFieldId="3" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{28C9493F-4EDC-4DEA-A069-2EABCC8221D9}" uniqueName="4" name="GridY" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{7039779C-43C8-4AF4-9E6C-5F591BC00B6B}" uniqueName="5" name="X" queryTableFieldId="5" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{F82C3927-F4B8-449B-8F9F-52F24BA96740}" uniqueName="6" name="Y" queryTableFieldId="6" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{C2067144-F640-41CF-B84F-43A7E5ABE6AD}" uniqueName="7" name="BaseLevel" queryTableFieldId="7" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{E4F7844C-45D3-413C-AA4C-0B574CCA7D71}" uniqueName="8" name="BaseOffset" queryTableFieldId="8"/>
-    <tableColumn id="9" xr3:uid="{43F2CC9C-33CF-4BF2-A790-D4ED540ECE49}" uniqueName="9" name="TopLevel" queryTableFieldId="9" dataDxfId="29"/>
-    <tableColumn id="10" xr3:uid="{E5FEB261-9C6B-41E7-822D-8C3D403AE21C}" uniqueName="10" name="TopOffset" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{4DBCB596-B53A-4F0A-A83E-208B045AC6A9}" uniqueName="11" name="Rotation" queryTableFieldId="11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FD210D4A-8F35-4202-A2DB-04840A11C937}" name="FOOTING_REBAR" displayName="FOOTING_REBAR" ref="A1:J11" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:J11" xr:uid="{FD210D4A-8F35-4202-A2DB-04840A11C937}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{69AA0B57-9AC3-40CF-9E7E-1B1BDA36FDFC}" uniqueName="1" name="TypeMark" queryTableFieldId="1" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{FAFA0DF1-D8AD-46D5-A054-F5351A0755BF}" uniqueName="2" name="Layer" queryTableFieldId="2" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{4C5CAD4B-0B7F-4816-A46F-722EFAC4B5B2}" uniqueName="3" name="Direction" queryTableFieldId="3" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{6308373A-3C6F-4154-9DEA-2EADA5D91642}" uniqueName="4" name="BarType" queryTableFieldId="4" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{DB18EAED-0474-4CF5-8131-C6CA37AD7BFB}" uniqueName="5" name="Diameter" queryTableFieldId="5"/>
+    <tableColumn id="6" xr3:uid="{8FB09626-1F5B-467B-918F-791DF536BF09}" uniqueName="6" name="Count" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{CA783AEC-AFDC-433D-BC88-DEA2D10F866D}" uniqueName="7" name="Spacing" queryTableFieldId="7"/>
+    <tableColumn id="8" xr3:uid="{E1416F18-9CEB-4635-A378-C10DA1F9BBA0}" uniqueName="8" name="ShapeCode" queryTableFieldId="8"/>
+    <tableColumn id="9" xr3:uid="{80CF4E90-46B9-4EE9-AB73-283061EBE3A4}" uniqueName="9" name="EndCover" queryTableFieldId="9"/>
+    <tableColumn id="10" xr3:uid="{DE04E247-6481-46C3-BEE4-C9D8C6CCD116}" uniqueName="10" name="Comments" queryTableFieldId="10" dataDxfId="15"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1116,6 +1113,340 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEDE508-7B76-40B3-948A-D7DA79BA7A0A}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>300</v>
+      </c>
+      <c r="C2">
+        <v>600</v>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3">
+        <v>400</v>
+      </c>
+      <c r="C3">
+        <v>400</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4">
+        <v>300</v>
+      </c>
+      <c r="C4">
+        <v>300</v>
+      </c>
+      <c r="D4">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E539A217-20EA-40A5-9C76-FE0C27D49BDC}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDF0A528-A4F5-4F87-BEE4-0C28A63A2B90}">
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1165,13 +1496,13 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>35</v>
       </c>
       <c r="D2">
@@ -1183,18 +1514,18 @@
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>37</v>
       </c>
       <c r="D3">
@@ -1206,18 +1537,18 @@
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>40</v>
       </c>
       <c r="D4">
@@ -1235,18 +1566,18 @@
       <c r="I4">
         <v>600</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>35</v>
       </c>
       <c r="D5">
@@ -1258,18 +1589,18 @@
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>40</v>
       </c>
       <c r="D6">
@@ -1287,18 +1618,18 @@
       <c r="I6">
         <v>500</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>37</v>
       </c>
       <c r="D7">
@@ -1310,18 +1641,18 @@
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>42</v>
       </c>
       <c r="D8">
@@ -1333,7 +1664,7 @@
       <c r="G8">
         <v>51</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1345,136 +1676,135 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DDA72C7-2611-4DAE-831B-42D1D6E5FF2E}">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="11.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="11.75" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="11.375" customWidth="1"/>
+    <col min="6" max="6" width="14.25" customWidth="1"/>
+    <col min="7" max="7" width="11.625" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="1" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1486,7 +1816,222 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE55F0F2-BC0E-4939-B58C-3BE3A6362F43}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>90</v>
+      </c>
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7">
+        <v>12500</v>
+      </c>
+      <c r="F7">
+        <v>8400</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA469F0-0A08-4A84-9E1C-686181FA02D5}">
   <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1536,16 +2081,16 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>37</v>
       </c>
       <c r="E2">
@@ -1563,21 +2108,21 @@
       <c r="I2">
         <v>50</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>37</v>
       </c>
       <c r="E3">
@@ -1595,21 +2140,21 @@
       <c r="I3">
         <v>50</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>70</v>
       </c>
       <c r="E4">
@@ -1624,21 +2169,21 @@
       <c r="I4">
         <v>50</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>70</v>
       </c>
       <c r="E5">
@@ -1653,21 +2198,21 @@
       <c r="I5">
         <v>50</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>37</v>
       </c>
       <c r="E6">
@@ -1685,21 +2230,21 @@
       <c r="I6">
         <v>50</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>37</v>
       </c>
       <c r="E7">
@@ -1717,21 +2262,21 @@
       <c r="I7">
         <v>50</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>35</v>
       </c>
       <c r="E8">
@@ -1749,21 +2294,21 @@
       <c r="I8">
         <v>50</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>35</v>
       </c>
       <c r="E9">
@@ -1781,21 +2326,21 @@
       <c r="I9">
         <v>50</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>37</v>
       </c>
       <c r="E10">
@@ -1810,21 +2355,21 @@
       <c r="I10">
         <v>50</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>37</v>
       </c>
       <c r="E11">
@@ -1839,557 +2384,8 @@
       <c r="I11">
         <v>50</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE55F0F2-BC0E-4939-B58C-3BE3A6362F43}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>51</v>
-      </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>90</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>12500</v>
-      </c>
-      <c r="F7">
-        <v>8400</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEDE508-7B76-40B3-948A-D7DA79BA7A0A}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2">
-        <v>300</v>
-      </c>
-      <c r="C2">
-        <v>600</v>
-      </c>
-      <c r="D2">
-        <v>40</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3">
-        <v>400</v>
-      </c>
-      <c r="C3">
-        <v>400</v>
-      </c>
-      <c r="D3">
-        <v>40</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
-        <v>300</v>
-      </c>
-      <c r="C4">
-        <v>300</v>
-      </c>
-      <c r="D4">
-        <v>40</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E539A217-20EA-40A5-9C76-FE0C27D49BDC}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="4.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
+      <c r="J11" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
